--- a/InputData/elec/BDTPTUMCF/Boolean Does This Plant Type Use Maximum Capacity Factor.xlsx
+++ b/InputData/elec/BDTPTUMCF/Boolean Does This Plant Type Use Maximum Capacity Factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\BDTPTUMCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97DCE9AD-342C-4F1D-9344-9510E0382F11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F782727-4A9D-4E77-9E54-B70F49E4C0AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2370" yWindow="1695" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="12" r:id="rId1"/>
@@ -365,6 +365,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Header Descriptions"/>
       <sheetName val="2019 NQC List"/>
@@ -386,6 +389,9 @@
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Information"/>
       <sheetName val="Request Type 1-2"/>
@@ -1047,7 +1053,7 @@
         <v>31</v>
       </c>
       <c r="B24" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">

--- a/InputData/elec/BDTPTUMCF/Boolean Does This Plant Type Use Maximum Capacity Factor.xlsx
+++ b/InputData/elec/BDTPTUMCF/Boolean Does This Plant Type Use Maximum Capacity Factor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\BDTPTUMCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F782727-4A9D-4E77-9E54-B70F49E4C0AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9155E55-ED50-4B58-B941-A8439ADDC1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="12" r:id="rId1"/>
@@ -55,9 +55,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
-    <t>natural gas nonpeaker</t>
-  </si>
-  <si>
     <t>nuclear</t>
   </si>
   <si>
@@ -73,9 +70,6 @@
     <t>biomass</t>
   </si>
   <si>
-    <t xml:space="preserve">geothermal </t>
-  </si>
-  <si>
     <t>petroleum</t>
   </si>
   <si>
@@ -152,6 +146,12 @@
   </si>
   <si>
     <t>hydrogen combined cycle</t>
+  </si>
+  <si>
+    <t>geothermal</t>
+  </si>
+  <si>
+    <t>natural gas peaker</t>
   </si>
 </sst>
 </file>
@@ -772,7 +772,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -780,10 +780,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E3" s="1"/>
       <c r="H3" s="1"/>
@@ -793,31 +793,31 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -845,14 +845,14 @@
   <sheetData>
     <row r="1" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="7"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B2" s="8">
         <v>1</v>
@@ -861,7 +861,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B3" s="8">
         <v>1</v>
@@ -870,7 +870,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B4" s="8">
         <v>1</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5" s="8">
         <v>0</v>
@@ -888,7 +888,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" s="8">
         <v>0</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" s="8">
         <v>0</v>
@@ -906,7 +906,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" s="8">
         <v>0</v>
@@ -915,7 +915,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" s="8">
         <v>0</v>
@@ -924,7 +924,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" s="8">
         <v>0</v>
@@ -933,7 +933,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="B11" s="8">
         <v>0</v>
@@ -942,7 +942,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B12" s="8">
         <v>1</v>
@@ -951,7 +951,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="B13" s="8">
         <v>1</v>
@@ -960,7 +960,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B14" s="8">
         <v>1</v>
@@ -969,7 +969,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B15" s="8">
         <v>0</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B16" s="8">
         <v>1</v>
@@ -987,7 +987,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B17" s="8">
         <v>1</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B18" s="8">
         <v>0</v>
@@ -1005,7 +1005,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B19" s="9">
         <f>B2</f>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B20" s="9">
         <f>B4</f>
@@ -1023,7 +1023,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B21" s="9">
         <f>B10</f>
@@ -1032,7 +1032,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B22" s="9">
         <f>B14</f>
@@ -1041,7 +1041,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B23" s="9">
         <f>B5</f>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B24" s="8">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B25">
         <v>1</v>

--- a/InputData/elec/BDTPTUMCF/Boolean Does This Plant Type Use Maximum Capacity Factor.xlsx
+++ b/InputData/elec/BDTPTUMCF/Boolean Does This Plant Type Use Maximum Capacity Factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\BDTPTUMCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97DCE9AD-342C-4F1D-9344-9510E0382F11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9155E55-ED50-4B58-B941-A8439ADDC1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2370" yWindow="1695" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="12" r:id="rId1"/>
@@ -55,9 +55,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
-    <t>natural gas nonpeaker</t>
-  </si>
-  <si>
     <t>nuclear</t>
   </si>
   <si>
@@ -73,9 +70,6 @@
     <t>biomass</t>
   </si>
   <si>
-    <t xml:space="preserve">geothermal </t>
-  </si>
-  <si>
     <t>petroleum</t>
   </si>
   <si>
@@ -152,6 +146,12 @@
   </si>
   <si>
     <t>hydrogen combined cycle</t>
+  </si>
+  <si>
+    <t>geothermal</t>
+  </si>
+  <si>
+    <t>natural gas peaker</t>
   </si>
 </sst>
 </file>
@@ -365,6 +365,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Header Descriptions"/>
       <sheetName val="2019 NQC List"/>
@@ -386,6 +389,9 @@
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Information"/>
       <sheetName val="Request Type 1-2"/>
@@ -766,7 +772,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -774,10 +780,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E3" s="1"/>
       <c r="H3" s="1"/>
@@ -787,31 +793,31 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -839,14 +845,14 @@
   <sheetData>
     <row r="1" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="7"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B2" s="8">
         <v>1</v>
@@ -855,7 +861,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B3" s="8">
         <v>1</v>
@@ -864,7 +870,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B4" s="8">
         <v>1</v>
@@ -873,7 +879,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5" s="8">
         <v>0</v>
@@ -882,7 +888,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" s="8">
         <v>0</v>
@@ -891,7 +897,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" s="8">
         <v>0</v>
@@ -900,7 +906,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" s="8">
         <v>0</v>
@@ -909,7 +915,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" s="8">
         <v>0</v>
@@ -918,7 +924,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" s="8">
         <v>0</v>
@@ -927,7 +933,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="B11" s="8">
         <v>0</v>
@@ -936,7 +942,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B12" s="8">
         <v>1</v>
@@ -945,7 +951,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="B13" s="8">
         <v>1</v>
@@ -954,7 +960,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B14" s="8">
         <v>1</v>
@@ -963,7 +969,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B15" s="8">
         <v>0</v>
@@ -972,7 +978,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B16" s="8">
         <v>1</v>
@@ -981,7 +987,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B17" s="8">
         <v>1</v>
@@ -990,7 +996,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B18" s="8">
         <v>0</v>
@@ -999,7 +1005,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B19" s="9">
         <f>B2</f>
@@ -1008,7 +1014,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B20" s="9">
         <f>B4</f>
@@ -1017,7 +1023,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B21" s="9">
         <f>B10</f>
@@ -1026,7 +1032,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B22" s="9">
         <f>B14</f>
@@ -1035,7 +1041,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B23" s="9">
         <f>B5</f>
@@ -1044,15 +1050,15 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B24" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B25">
         <v>1</v>
